--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-accession-number-identifier.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-accession-number-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:55:35+00:00</t>
+    <t>2026-09-16T07:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>DataType définissant l'Accession Number d'une demande d'examen. Il s'agit d'un identifiant unique attribué à chaque demande d'examen.</t>
+    <t>DataType définissant l'Accession Number d'une demande d'examen. Il s'agit d'un identifiant unique attribué à chaque demande d'examen d'imagerie.</t>
   </si>
   <si>
     <t>Purpose</t>
